--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:55:51</t>
+          <t>Última actualización: 03:58:59</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -499,6 +499,31 @@
         <v>67</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>03:58:43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05:11</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>73</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -528,7 +553,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:55:51</t>
+          <t>Última actualización: 03:58:59</t>
         </is>
       </c>
     </row>
@@ -563,7 +588,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 01:55:51</t>
+          <t>Última actualización: 03:58:59</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:58:59</t>
+          <t>Última actualización: 04:28:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -524,6 +524,31 @@
         <v>73</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>04:27:49</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>05:44</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>77</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -553,7 +578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:58:59</t>
+          <t>Última actualización: 04:28:05</t>
         </is>
       </c>
     </row>
@@ -588,7 +613,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 03:58:59</t>
+          <t>Última actualización: 04:28:05</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:28:05</t>
+          <t>Última actualización: 04:43:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -549,6 +549,31 @@
         <v>77</v>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>04:43:01</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>05:12</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>29</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -578,7 +603,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:28:05</t>
+          <t>Última actualización: 04:43:18</t>
         </is>
       </c>
     </row>
@@ -613,7 +638,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:28:05</t>
+          <t>Última actualización: 04:43:18</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:43:18</t>
+          <t>Última actualización: 04:55:20</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -574,6 +574,56 @@
         <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>04:55:04</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>05:52</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>57</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>04:55:04</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>96</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -603,7 +653,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:43:18</t>
+          <t>Última actualización: 04:55:20</t>
         </is>
       </c>
     </row>
@@ -638,7 +688,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:43:18</t>
+          <t>Última actualización: 04:55:20</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:20</t>
+          <t>Última actualización: 05:31:42</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -624,6 +624,81 @@
         <v>96</v>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>05:31:26</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>30</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>05:31:26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>83</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>05:31:26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>90</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -653,7 +728,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:20</t>
+          <t>Última actualización: 05:31:42</t>
         </is>
       </c>
     </row>
@@ -688,7 +763,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 04:55:20</t>
+          <t>Última actualización: 05:31:42</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:31:42</t>
+          <t>Última actualización: 05:57:23</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:31:42</t>
+          <t>Última actualización: 05:57:23</t>
         </is>
       </c>
     </row>
@@ -763,7 +763,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:31:42</t>
+          <t>Última actualización: 05:57:23</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:57:23</t>
+          <t>Última actualización: 06:29:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -699,6 +699,231 @@
         <v>90</v>
       </c>
       <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>06:53</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>25</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>32</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>07:13</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>45</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>47</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>67</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>83</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>07:58</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>90</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>06:28:56</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>08:01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>93</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -728,7 +953,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:57:23</t>
+          <t>Última actualización: 06:29:08</t>
         </is>
       </c>
     </row>
@@ -750,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,14 +988,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 05:57:23</t>
+          <t>Última actualización: 06:29:08</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06:29:07</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>60</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:29:08</t>
+          <t>Última actualización: 06:45:18</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 18</t>
+          <t>Total filas: 24</t>
         </is>
       </c>
     </row>
@@ -924,6 +924,156 @@
         <v>93</v>
       </c>
       <c r="E23" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>07:14</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>29</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>07:16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>31</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>07:29</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>51</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>77</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>06:45:06</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>84</v>
+      </c>
+      <c r="E29" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -953,7 +1103,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:29:08</t>
+          <t>Última actualización: 06:45:18</t>
         </is>
       </c>
     </row>
@@ -988,7 +1138,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:29:08</t>
+          <t>Última actualización: 06:45:18</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:45:18</t>
+          <t>Última actualización: 06:56:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 24</t>
+          <t>Total filas: 29</t>
         </is>
       </c>
     </row>
@@ -1074,6 +1074,131 @@
         <v>84</v>
       </c>
       <c r="E29" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>25</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>40</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>67</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>08:04</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>68</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>93</v>
+      </c>
+      <c r="E34" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1090,7 +1215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1103,14 +1228,66 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:45:18</t>
+          <t>Última actualización: 06:56:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 0</t>
+          <t>Total filas: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Scrap</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Hora_Llegada</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Línea</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Minutos</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Parada</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>06:56:32</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>25</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,14 +1315,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:45:18</t>
+          <t>Última actualización: 06:56:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -1196,6 +1373,31 @@
         <v>60</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>06:56:43</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>32</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E34"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:56:43</t>
+          <t>Última actualización: 07:27:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 29</t>
+          <t>Total filas: 37</t>
         </is>
       </c>
     </row>
@@ -1199,6 +1199,206 @@
         <v>93</v>
       </c>
       <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>07:33</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>6</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>08:11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>44</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>47</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>77</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>08:56</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>89</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>95</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>07:27:28</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>96</v>
+      </c>
+      <c r="E42" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1228,7 +1428,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:56:43</t>
+          <t>Última actualización: 07:27:35</t>
         </is>
       </c>
     </row>
@@ -1302,7 +1502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1315,14 +1515,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 06:56:43</t>
+          <t>Última actualización: 07:27:35</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1398,6 +1598,56 @@
         <v>32</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07:27:32</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>57</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>07:27:35</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>08:25</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>58</v>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:35</t>
+          <t>Última actualización: 07:46:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 37</t>
+          <t>Total filas: 41</t>
         </is>
       </c>
     </row>
@@ -1399,6 +1399,106 @@
         <v>96</v>
       </c>
       <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>07:46:45</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>69</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>07:46:45</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>74</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>07:46:45</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>09:14</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>88</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>07:46:45</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>90</v>
+      </c>
+      <c r="E46" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1428,7 +1528,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:35</t>
+          <t>Última actualización: 07:46:52</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1515,14 +1615,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:27:35</t>
+          <t>Última actualización: 07:46:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 7</t>
         </is>
       </c>
     </row>
@@ -1648,6 +1748,81 @@
         <v>58</v>
       </c>
       <c r="E9" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>07:46:49</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>36</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>07:46:52</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08:22</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>36</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>07:46:52</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>66</v>
+      </c>
+      <c r="E12" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:52</t>
+          <t>Última actualización: 08:20:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 41</t>
+          <t>Total filas: 54</t>
         </is>
       </c>
     </row>
@@ -1499,6 +1499,331 @@
         <v>90</v>
       </c>
       <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>13</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>08:51</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>31</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>48</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>55</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>57</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>61</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>67</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>69</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>71</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>09:39</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>79</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>85</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>90</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>09:51</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>91</v>
+      </c>
+      <c r="E59" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1515,7 +1840,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1528,14 +1853,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:52</t>
+          <t>Última actualización: 08:20:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 2</t>
         </is>
       </c>
     </row>
@@ -1586,6 +1911,31 @@
         <v>25</v>
       </c>
       <c r="E6" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>08:20:08</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>09:27</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1602,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1615,14 +1965,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 07:46:52</t>
+          <t>Última actualización: 08:20:15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 7</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -1825,6 +2175,31 @@
       <c r="E12" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>08:20:12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:20:15</t>
+          <t>Última actualización: 08:40:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 54</t>
+          <t>Total filas: 60</t>
         </is>
       </c>
     </row>
@@ -1824,6 +1824,156 @@
         <v>91</v>
       </c>
       <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>49</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>09:33</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>53</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>80</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>83</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>84</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>95</v>
+      </c>
+      <c r="E65" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1840,7 +1990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1853,14 +2003,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:20:15</t>
+          <t>Última actualización: 08:40:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 2</t>
+          <t>Total filas: 3</t>
         </is>
       </c>
     </row>
@@ -1936,6 +2086,31 @@
         <v>67</v>
       </c>
       <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>08:40:16</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>83</v>
+      </c>
+      <c r="E8" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1952,7 +2127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1965,14 +2140,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:20:15</t>
+          <t>Última actualización: 08:40:23</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -2198,6 +2373,31 @@
         <v>3</v>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>08:40:20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>89</v>
+      </c>
+      <c r="E14" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E65"/>
+  <dimension ref="A1:E74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:40:23</t>
+          <t>Última actualización: 08:52:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 60</t>
+          <t>Total filas: 69</t>
         </is>
       </c>
     </row>
@@ -1974,6 +1974,231 @@
         <v>95</v>
       </c>
       <c r="E65" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>34</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>09:41</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>49</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>09:44</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>52</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>57</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>70</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>82</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>90</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>10:26</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>94</v>
+      </c>
+      <c r="E74" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -1990,7 +2215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2003,14 +2228,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:40:23</t>
+          <t>Última actualización: 08:52:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 3</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -2111,6 +2336,56 @@
         <v>83</v>
       </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215_EL PELIGRO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>34</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>08:52:47</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>10:02</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>70</v>
+      </c>
+      <c r="E10" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2127,7 +2402,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2140,14 +2415,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:40:23</t>
+          <t>Última actualización: 08:52:53</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -2400,6 +2675,56 @@
       <c r="E14" t="inlineStr">
         <is>
           <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>08:52:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>76</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>08:52:53</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10:22</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>90</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:52:53</t>
+          <t>Última actualización: 09:48:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 69</t>
+          <t>Total filas: 85</t>
         </is>
       </c>
     </row>
@@ -2199,6 +2199,406 @@
         <v>94</v>
       </c>
       <c r="E74" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>09:54</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>6</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>13</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>15</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>10:14</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>26</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>36</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>10:25</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>37</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>44</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>10:34</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>46</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>10:44</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>56</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>10:49</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>61</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>63</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>74</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>75</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>76</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>83</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>09:48:28</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>97</v>
+      </c>
+      <c r="E90" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2228,7 +2628,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:52:53</t>
+          <t>Última actualización: 09:48:34</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2802,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2415,14 +2815,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 08:52:53</t>
+          <t>Última actualización: 09:48:34</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -2723,6 +3123,56 @@
         <v>90</v>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>09:48:34</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>35</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>09:48:34</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10:31</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>43</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E90"/>
+  <dimension ref="A1:E104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:48:34</t>
+          <t>Última actualización: 10:32:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 85</t>
+          <t>Total filas: 99</t>
         </is>
       </c>
     </row>
@@ -2599,6 +2599,356 @@
         <v>97</v>
       </c>
       <c r="E90" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>10:39</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>7</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>22</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>25</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>29</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>11:03</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>31</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>33</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>11:09</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>37</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>62</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>62</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>63</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>68</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>82</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>93</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>95</v>
+      </c>
+      <c r="E104" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2615,7 +2965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2628,14 +2978,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:48:34</t>
+          <t>Última actualización: 10:32:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 5</t>
+          <t>Total filas: 6</t>
         </is>
       </c>
     </row>
@@ -2786,6 +3136,31 @@
         <v>70</v>
       </c>
       <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10:32:15</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>68</v>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2802,7 +3177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2815,14 +3190,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 09:48:34</t>
+          <t>Última actualización: 10:32:21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -3175,6 +3550,31 @@
       <c r="E18" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>10:32:18</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>72</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E104"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:32:21</t>
+          <t>Última actualización: 10:53:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 99</t>
+          <t>Total filas: 111</t>
         </is>
       </c>
     </row>
@@ -2949,6 +2949,306 @@
         <v>95</v>
       </c>
       <c r="E104" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>10:56</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>38</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>40</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>40</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>51</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>52</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>60</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>68</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>73</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>84</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>95</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>12:31</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>98</v>
+      </c>
+      <c r="E116" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -2965,7 +3265,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2978,14 +3278,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:32:21</t>
+          <t>Última actualización: 10:53:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 8</t>
         </is>
       </c>
     </row>
@@ -3161,6 +3461,56 @@
         <v>68</v>
       </c>
       <c r="E11" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>11:44</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>51</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10:53:38</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>12:28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>95</v>
+      </c>
+      <c r="E13" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3177,7 +3527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3190,14 +3540,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:32:21</t>
+          <t>Última actualización: 10:53:50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -3573,6 +3923,31 @@
         <v>72</v>
       </c>
       <c r="E19" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>10:53:42</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>11:43</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E20" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E116"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:50</t>
+          <t>Última actualización: 11:23:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 111</t>
+          <t>Total filas: 123</t>
         </is>
       </c>
     </row>
@@ -3249,6 +3249,306 @@
         <v>98</v>
       </c>
       <c r="E116" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>17</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>11:52</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>30</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>35</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>41</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>12:04</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>42</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>12:16</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>54</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>55</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>68</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>12:39</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>77</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>80</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>88</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>98</v>
+      </c>
+      <c r="E128" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3265,7 +3565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3278,14 +3578,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:50</t>
+          <t>Última actualización: 11:23:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 8</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -3511,6 +3811,56 @@
         <v>95</v>
       </c>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215A_EL PATO</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>17</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>11:22:59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>98</v>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3527,7 +3877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3540,14 +3890,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 10:53:50</t>
+          <t>Última actualización: 11:23:10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 15</t>
+          <t>Total filas: 16</t>
         </is>
       </c>
     </row>
@@ -3948,6 +4298,31 @@
         <v>50</v>
       </c>
       <c r="E20" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11:23:02</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>12:44</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>81</v>
+      </c>
+      <c r="E21" t="inlineStr">
         <is>
           <t>L6203</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E128"/>
+  <dimension ref="A1:E137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:23:10</t>
+          <t>Última actualización: 11:44:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 123</t>
+          <t>Total filas: 132</t>
         </is>
       </c>
     </row>
@@ -3549,6 +3549,231 @@
         <v>98</v>
       </c>
       <c r="E128" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>25</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>26</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>78</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>82</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>83</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>88</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>95</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>97</v>
+      </c>
+      <c r="E137" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3565,7 +3790,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3578,14 +3803,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:23:10</t>
+          <t>Última actualización: 11:44:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 10</t>
+          <t>Total filas: 11</t>
         </is>
       </c>
     </row>
@@ -3861,6 +4086,31 @@
         <v>98</v>
       </c>
       <c r="E15" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>11:43:59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>11:46</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3877,7 +4127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3890,14 +4140,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:23:10</t>
+          <t>Última actualización: 11:44:05</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 16</t>
+          <t>Total filas: 17</t>
         </is>
       </c>
     </row>
@@ -4325,6 +4575,31 @@
       <c r="E21" t="inlineStr">
         <is>
           <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>11:44:05</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>13:09</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>85</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>L6173</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E137"/>
+  <dimension ref="A1:E146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:44:05</t>
+          <t>Última actualización: 11:56:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 132</t>
+          <t>Total filas: 141</t>
         </is>
       </c>
     </row>
@@ -3774,6 +3774,231 @@
         <v>97</v>
       </c>
       <c r="E137" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>225_GOMEZ</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>7</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>12:06</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>33</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>15X38_ABASTO</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>44</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>12:51</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>55</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>62</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>71</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>85</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>94</v>
+      </c>
+      <c r="E146" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -3790,7 +4015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3803,14 +4028,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:44:05</t>
+          <t>Última actualización: 11:56:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 11</t>
+          <t>Total filas: 12</t>
         </is>
       </c>
     </row>
@@ -4111,6 +4336,31 @@
         <v>3</v>
       </c>
       <c r="E16" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>11:56:17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>12:29</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>33</v>
+      </c>
+      <c r="E17" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -4127,7 +4377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4140,14 +4390,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:44:05</t>
+          <t>Última actualización: 11:56:24</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 17</t>
+          <t>Total filas: 18</t>
         </is>
       </c>
     </row>
@@ -4598,6 +4848,31 @@
         <v>85</v>
       </c>
       <c r="E22" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>11:56:23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>78</v>
+      </c>
+      <c r="E23" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E146"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:56:24</t>
+          <t>Última actualización: 12:25:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 141</t>
+          <t>Total filas: 149</t>
         </is>
       </c>
     </row>
@@ -3999,6 +3999,206 @@
         <v>94</v>
       </c>
       <c r="E146" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>36</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>38</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>13:07</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>42</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>54</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>56</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>74</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>86</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>96</v>
+      </c>
+      <c r="E154" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -4015,7 +4215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4028,14 +4228,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:56:24</t>
+          <t>Última actualización: 12:25:17</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 12</t>
+          <t>Total filas: 13</t>
         </is>
       </c>
     </row>
@@ -4361,6 +4561,31 @@
         <v>33</v>
       </c>
       <c r="E17" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>12:25:11</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>13:01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>36</v>
+      </c>
+      <c r="E18" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -4390,7 +4615,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 11:56:24</t>
+          <t>Última actualización: 12:25:17</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:25:17</t>
+          <t>Última actualización: 12:42:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 149</t>
+          <t>Total filas: 150</t>
         </is>
       </c>
     </row>
@@ -4199,6 +4199,31 @@
         <v>96</v>
       </c>
       <c r="E154" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>12:42:37</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>55</v>
+      </c>
+      <c r="E155" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -4228,7 +4253,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:25:17</t>
+          <t>Última actualización: 12:42:43</t>
         </is>
       </c>
     </row>
@@ -4602,7 +4627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E23"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4615,14 +4640,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:25:17</t>
+          <t>Última actualización: 12:42:43</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 18</t>
+          <t>Total filas: 21</t>
         </is>
       </c>
     </row>
@@ -5098,6 +5123,81 @@
         <v>78</v>
       </c>
       <c r="E23" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>12:42:40</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>71</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>12:42:43</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>26</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>12:42:43</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>31</v>
+      </c>
+      <c r="E26" t="inlineStr">
         <is>
           <t>L6173</t>
         </is>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E155"/>
+  <dimension ref="A1:E160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:43</t>
+          <t>Última actualización: 12:55:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 150</t>
+          <t>Total filas: 155</t>
         </is>
       </c>
     </row>
@@ -4224,6 +4224,131 @@
         <v>55</v>
       </c>
       <c r="E155" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>9</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>39</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>56</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>90</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>12:55:00</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>99</v>
+      </c>
+      <c r="E160" t="inlineStr">
         <is>
           <t>LP1912</t>
         </is>
@@ -4253,7 +4378,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:43</t>
+          <t>Última actualización: 12:55:07</t>
         </is>
       </c>
     </row>
@@ -4627,7 +4752,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4640,14 +4765,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:42:43</t>
+          <t>Última actualización: 12:55:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 21</t>
+          <t>Total filas: 22</t>
         </is>
       </c>
     </row>
@@ -5200,6 +5325,31 @@
       <c r="E26" t="inlineStr">
         <is>
           <t>L6173</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>12:55:04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>59</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>L6203</t>
         </is>
       </c>
     </row>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E160"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:55:07</t>
+          <t>Última actualización: 13:28:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 155</t>
+          <t>Total filas: 164</t>
         </is>
       </c>
     </row>
@@ -478,6 +478,11 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -503,6 +508,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -528,6 +534,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -553,6 +560,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -578,6 +586,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -603,6 +612,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -628,6 +638,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -653,6 +664,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -678,6 +690,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -703,6 +716,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -728,6 +742,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -753,6 +768,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -778,6 +794,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -803,6 +820,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -828,6 +846,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -853,6 +872,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -878,6 +898,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -903,6 +924,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -928,6 +950,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -953,6 +976,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -978,6 +1002,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1003,6 +1028,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1028,6 +1054,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1053,6 +1080,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1078,6 +1106,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1103,6 +1132,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1128,6 +1158,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1153,6 +1184,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1178,6 +1210,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1203,6 +1236,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1228,6 +1262,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1253,6 +1288,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1278,6 +1314,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1303,6 +1340,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1328,6 +1366,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1353,6 +1392,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1378,6 +1418,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1403,6 +1444,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1428,6 +1470,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1453,6 +1496,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1478,6 +1522,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1503,6 +1548,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1528,6 +1574,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1553,6 +1600,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1578,6 +1626,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1603,6 +1652,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1628,6 +1678,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1653,6 +1704,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1678,6 +1730,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1703,6 +1756,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1728,6 +1782,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1753,6 +1808,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1778,6 +1834,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1803,6 +1860,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1828,6 +1886,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1853,6 +1912,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1878,6 +1938,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1903,6 +1964,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1928,6 +1990,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1953,6 +2016,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1978,6 +2042,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2003,6 +2068,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2028,6 +2094,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2053,6 +2120,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2078,6 +2146,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2103,6 +2172,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2128,6 +2198,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2153,6 +2224,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2178,6 +2250,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2203,6 +2276,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2228,6 +2302,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2253,6 +2328,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2278,6 +2354,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2303,6 +2380,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2328,6 +2406,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2353,6 +2432,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2378,6 +2458,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2403,6 +2484,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2428,6 +2510,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2453,6 +2536,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2478,6 +2562,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2503,6 +2588,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2528,6 +2614,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2553,6 +2640,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2578,6 +2666,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2603,6 +2692,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2628,6 +2718,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2653,6 +2744,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2678,6 +2770,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2703,6 +2796,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2728,6 +2822,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2753,6 +2848,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2778,6 +2874,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2803,6 +2900,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2828,6 +2926,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2853,6 +2952,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2878,6 +2978,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2903,6 +3004,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2928,6 +3030,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2953,6 +3056,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2978,6 +3082,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3003,6 +3108,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3028,6 +3134,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3053,6 +3160,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3078,6 +3186,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3103,6 +3212,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3128,6 +3238,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3153,6 +3264,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3178,6 +3290,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3203,6 +3316,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3228,6 +3342,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3253,6 +3368,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3278,6 +3394,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3303,6 +3420,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3328,6 +3446,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3353,6 +3472,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3378,6 +3498,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3403,6 +3524,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3428,6 +3550,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3453,6 +3576,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3478,6 +3602,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3503,6 +3628,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3528,6 +3654,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3553,6 +3680,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3578,6 +3706,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3603,6 +3732,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3628,6 +3758,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3653,6 +3784,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3678,6 +3810,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3703,6 +3836,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3728,6 +3862,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3753,6 +3888,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3778,6 +3914,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3803,6 +3940,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3828,6 +3966,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3853,6 +3992,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3878,6 +4018,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -3903,6 +4044,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3928,6 +4070,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3953,6 +4096,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3978,6 +4122,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -4003,6 +4148,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -4028,6 +4174,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -4053,6 +4200,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -4078,6 +4226,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -4103,6 +4252,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -4128,6 +4278,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -4153,6 +4304,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -4178,6 +4330,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -4203,6 +4356,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -4228,6 +4382,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -4253,6 +4408,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -4278,6 +4434,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -4303,6 +4460,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -4328,6 +4486,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -4353,6 +4512,241 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>5</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>33</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>43</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>45</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>69</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>70</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>17X38_ROMERO</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>72</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>77</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>97</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4365,7 +4759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4378,14 +4772,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:55:07</t>
+          <t>Última actualización: 13:28:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 13</t>
+          <t>Total filas: 14</t>
         </is>
       </c>
     </row>
@@ -4415,6 +4809,11 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4440,6 +4839,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4465,6 +4865,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4490,6 +4891,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4515,6 +4917,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4540,6 +4943,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4565,6 +4969,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4590,6 +4995,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4615,6 +5021,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4640,6 +5047,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4665,6 +5073,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4690,6 +5099,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4715,6 +5125,7 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4740,6 +5151,33 @@
           <t>LP1912</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>13:28:17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>77</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4752,7 +5190,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4765,14 +5203,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:55:07</t>
+          <t>Última actualización: 13:28:29</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 22</t>
+          <t>Total filas: 23</t>
         </is>
       </c>
     </row>
@@ -4802,6 +5240,11 @@
           <t>Parada</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>CodigoColectivo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4827,6 +5270,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -4852,6 +5296,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -4877,6 +5322,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4902,6 +5348,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4927,6 +5374,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4952,6 +5400,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4977,6 +5426,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5002,6 +5452,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5027,6 +5478,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5052,6 +5504,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5077,6 +5530,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5102,6 +5556,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5127,6 +5582,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5152,6 +5608,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5177,6 +5634,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5202,6 +5660,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5227,6 +5686,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5252,6 +5712,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5277,6 +5738,7 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -5302,6 +5764,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -5327,6 +5790,7 @@
           <t>L6173</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -5352,6 +5816,33 @@
           <t>L6203</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>13:28:21</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>66</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:28:29</t>
+          <t>Última actualización: 13:35:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 164</t>
+          <t>Total filas: 169</t>
         </is>
       </c>
     </row>
@@ -4747,6 +4747,156 @@
         </is>
       </c>
       <c r="F169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>032</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>49</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>027</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>50</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>022</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>69</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>89</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>006</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4759,7 +4909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4772,14 +4922,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:28:29</t>
+          <t>Última actualización: 13:35:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 14</t>
+          <t>Total filas: 15</t>
         </is>
       </c>
     </row>
@@ -5178,6 +5328,36 @@
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>13:35:44</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>69</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5190,7 +5370,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5203,14 +5383,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:28:29</t>
+          <t>Última actualización: 13:35:52</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 23</t>
+          <t>Total filas: 25</t>
         </is>
       </c>
     </row>
@@ -5843,6 +6023,66 @@
         </is>
       </c>
       <c r="F28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>13:35:48</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>58</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>13:35:52</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>14:56</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>81</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/horarios-141-2026-01-10.xlsx
+++ b/horarios-141-2026-01-10.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F174"/>
+  <dimension ref="A1:F175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:52</t>
+          <t>Última actualización: 13:38:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 169</t>
+          <t>Total filas: 170</t>
         </is>
       </c>
     </row>
@@ -4772,10 +4772,8 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>032</t>
-        </is>
+      <c r="F170" t="n">
+        <v>32</v>
       </c>
     </row>
     <row r="171">
@@ -4802,10 +4800,8 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>027</t>
-        </is>
+      <c r="F171" t="n">
+        <v>27</v>
       </c>
     </row>
     <row r="172">
@@ -4832,10 +4828,8 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>022</t>
-        </is>
+      <c r="F172" t="n">
+        <v>22</v>
       </c>
     </row>
     <row r="173">
@@ -4862,10 +4856,8 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="F173" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="174">
@@ -4892,11 +4884,35 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>006</t>
-        </is>
-      </c>
+      <c r="F174" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>13:38:14</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>61</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4922,7 +4938,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:52</t>
+          <t>Última actualización: 13:38:22</t>
         </is>
       </c>
     </row>
@@ -5353,10 +5369,8 @@
           <t>LP1912</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
+      <c r="F20" t="n">
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -5370,7 +5384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5383,14 +5397,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 13:35:52</t>
+          <t>Última actualización: 13:38:22</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 25</t>
+          <t>Total filas: 26</t>
         </is>
       </c>
     </row>
@@ -6048,10 +6062,8 @@
           <t>L6203</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
+      <c r="F29" t="n">
+        <v>211</v>
       </c>
     </row>
     <row r="30">
@@ -6078,11 +6090,35 @@
           <t>L6173</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
+      <c r="F30" t="n">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>13:38:22</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>79</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
